--- a/162.xlsx
+++ b/162.xlsx
@@ -511,7 +511,7 @@
         <v>1.899414658546448</v>
       </c>
       <c r="K2" t="n">
-        <v>1.109919999998965e-05</v>
+        <v>1.121389999934763e-05</v>
       </c>
     </row>
     <row r="3">
@@ -552,7 +552,7 @@
         <v>2.021719694137573</v>
       </c>
       <c r="K3" t="n">
-        <v>7.339300000239746e-06</v>
+        <v>7.045399999697111e-06</v>
       </c>
     </row>
     <row r="4">
@@ -593,7 +593,7 @@
         <v>2.23393440246582</v>
       </c>
       <c r="K4" t="n">
-        <v>7.33349999973143e-06</v>
+        <v>8.152099999279017e-06</v>
       </c>
     </row>
     <row r="5">
@@ -634,7 +634,7 @@
         <v>1.836353302001953</v>
       </c>
       <c r="K5" t="n">
-        <v>7.124400000066089e-06</v>
+        <v>6.83740000022226e-06</v>
       </c>
     </row>
     <row r="6">
@@ -675,7 +675,7 @@
         <v>2.534233093261719</v>
       </c>
       <c r="K6" t="n">
-        <v>7.877100000769133e-06</v>
+        <v>7.04550000045856e-06</v>
       </c>
     </row>
     <row r="7">
@@ -716,7 +716,7 @@
         <v>0.6462885141372681</v>
       </c>
       <c r="K7" t="n">
-        <v>7.241100000101142e-06</v>
+        <v>7.471099999747821e-06</v>
       </c>
     </row>
     <row r="8">
@@ -757,7 +757,7 @@
         <v>0.6290862560272217</v>
       </c>
       <c r="K8" t="n">
-        <v>6.924399999661546e-06</v>
+        <v>7.983800000147312e-06</v>
       </c>
     </row>
     <row r="9">
@@ -798,7 +798,7 @@
         <v>0.6569992899894714</v>
       </c>
       <c r="K9" t="n">
-        <v>7.144999999582069e-06</v>
+        <v>7.413499999529449e-06</v>
       </c>
     </row>
     <row r="10">
@@ -839,7 +839,7 @@
         <v>0.6297457814216614</v>
       </c>
       <c r="K10" t="n">
-        <v>6.860399999823131e-06</v>
+        <v>7.94580000001588e-06</v>
       </c>
     </row>
     <row r="11">
@@ -880,7 +880,7 @@
         <v>0.612906277179718</v>
       </c>
       <c r="K11" t="n">
-        <v>7.44600000052742e-06</v>
+        <v>7.377899999482907e-06</v>
       </c>
     </row>
     <row r="12">
@@ -921,7 +921,7 @@
         <v>0.6798930764198303</v>
       </c>
       <c r="K12" t="n">
-        <v>7.245599999805563e-06</v>
+        <v>6.789299999581999e-06</v>
       </c>
     </row>
     <row r="13">
@@ -962,7 +962,7 @@
         <v>0.6647471785545349</v>
       </c>
       <c r="K13" t="n">
-        <v>7.193899999947462e-06</v>
+        <v>7.426300000588526e-06</v>
       </c>
     </row>
     <row r="14">
@@ -1003,7 +1003,7 @@
         <v>0.6927752494812012</v>
       </c>
       <c r="K14" t="n">
-        <v>7.049400000141759e-06</v>
+        <v>7.91879999997036e-06</v>
       </c>
     </row>
     <row r="15">
@@ -1044,7 +1044,7 @@
         <v>0.6775802373886108</v>
       </c>
       <c r="K15" t="n">
-        <v>7.191400000010617e-06</v>
+        <v>7.305999999516643e-06</v>
       </c>
     </row>
     <row r="16">
@@ -1085,7 +1085,7 @@
         <v>0.6975191235542297</v>
       </c>
       <c r="K16" t="n">
-        <v>1.520700000037323e-05</v>
+        <v>6.926300000486663e-06</v>
       </c>
     </row>
     <row r="17">
@@ -1126,7 +1126,7 @@
         <v>0.8259356021881104</v>
       </c>
       <c r="K17" t="n">
-        <v>1.396999999997206e-05</v>
+        <v>1.514829999905487e-05</v>
       </c>
     </row>
     <row r="18">
@@ -1167,7 +1167,7 @@
         <v>0.7692122459411621</v>
       </c>
       <c r="K18" t="n">
-        <v>1.390829999945709e-05</v>
+        <v>1.383190000160539e-05</v>
       </c>
     </row>
     <row r="19">
@@ -1208,7 +1208,7 @@
         <v>0.7609123587608337</v>
       </c>
       <c r="K19" t="n">
-        <v>1.357180000013614e-05</v>
+        <v>1.58119000006991e-05</v>
       </c>
     </row>
     <row r="20">
@@ -1249,7 +1249,7 @@
         <v>0.8261111378669739</v>
       </c>
       <c r="K20" t="n">
-        <v>1.402340000004187e-05</v>
+        <v>1.396920000115642e-05</v>
       </c>
     </row>
     <row r="21">
@@ -1290,7 +1290,7 @@
         <v>0.7763814330101013</v>
       </c>
       <c r="K21" t="n">
-        <v>1.332749999983207e-05</v>
+        <v>1.828459999887855e-05</v>
       </c>
     </row>
     <row r="22">
@@ -1331,7 +1331,7 @@
         <v>0.6375079751014709</v>
       </c>
       <c r="K22" t="n">
-        <v>1.352979999956005e-05</v>
+        <v>1.401409999925818e-05</v>
       </c>
     </row>
     <row r="23">
@@ -1372,7 +1372,7 @@
         <v>0.6591068506240845</v>
       </c>
       <c r="K23" t="n">
-        <v>1.372150000042893e-05</v>
+        <v>1.420580000012706e-05</v>
       </c>
     </row>
     <row r="24">
@@ -1413,7 +1413,7 @@
         <v>0.6344265937805176</v>
       </c>
       <c r="K24" t="n">
-        <v>1.388169999972888e-05</v>
+        <v>1.398140000128478e-05</v>
       </c>
     </row>
     <row r="25">
@@ -1454,7 +1454,7 @@
         <v>0.7032672762870789</v>
       </c>
       <c r="K25" t="n">
-        <v>1.375490000009449e-05</v>
+        <v>1.371109999854525e-05</v>
       </c>
     </row>
     <row r="26">
@@ -1495,7 +1495,7 @@
         <v>0.7030646800994873</v>
       </c>
       <c r="K26" t="n">
-        <v>1.35126000004675e-05</v>
+        <v>1.401950000035868e-05</v>
       </c>
     </row>
   </sheetData>

--- a/162.xlsx
+++ b/162.xlsx
@@ -511,7 +511,7 @@
         <v>1.899414658546448</v>
       </c>
       <c r="K2" t="n">
-        <v>1.121389999934763e-05</v>
+        <v>1.346120000016526e-05</v>
       </c>
     </row>
     <row r="3">
@@ -552,7 +552,7 @@
         <v>2.021719694137573</v>
       </c>
       <c r="K3" t="n">
-        <v>7.045399999697111e-06</v>
+        <v>8.164099999703468e-06</v>
       </c>
     </row>
     <row r="4">
@@ -593,7 +593,7 @@
         <v>2.23393440246582</v>
       </c>
       <c r="K4" t="n">
-        <v>8.152099999279017e-06</v>
+        <v>8.393999999952938e-06</v>
       </c>
     </row>
     <row r="5">
@@ -634,7 +634,7 @@
         <v>1.836353302001953</v>
       </c>
       <c r="K5" t="n">
-        <v>6.83740000022226e-06</v>
+        <v>7.823599999937869e-06</v>
       </c>
     </row>
     <row r="6">
@@ -675,7 +675,7 @@
         <v>2.534233093261719</v>
       </c>
       <c r="K6" t="n">
-        <v>7.04550000045856e-06</v>
+        <v>8.343599999989237e-06</v>
       </c>
     </row>
     <row r="7">
@@ -716,7 +716,7 @@
         <v>0.6462885141372681</v>
       </c>
       <c r="K7" t="n">
-        <v>7.471099999747821e-06</v>
+        <v>8.053900000049906e-06</v>
       </c>
     </row>
     <row r="8">
@@ -757,7 +757,7 @@
         <v>0.6290862560272217</v>
       </c>
       <c r="K8" t="n">
-        <v>7.983800000147312e-06</v>
+        <v>1.021799999989526e-05</v>
       </c>
     </row>
     <row r="9">
@@ -798,7 +798,7 @@
         <v>0.6569992899894714</v>
       </c>
       <c r="K9" t="n">
-        <v>7.413499999529449e-06</v>
+        <v>7.827399999769113e-06</v>
       </c>
     </row>
     <row r="10">
@@ -839,7 +839,7 @@
         <v>0.6297457814216614</v>
       </c>
       <c r="K10" t="n">
-        <v>7.94580000001588e-06</v>
+        <v>8.007699999780015e-06</v>
       </c>
     </row>
     <row r="11">
@@ -880,7 +880,7 @@
         <v>0.612906277179718</v>
       </c>
       <c r="K11" t="n">
-        <v>7.377899999482907e-06</v>
+        <v>1.599919999989652e-05</v>
       </c>
     </row>
     <row r="12">
@@ -921,7 +921,7 @@
         <v>0.6798930764198303</v>
       </c>
       <c r="K12" t="n">
-        <v>6.789299999581999e-06</v>
+        <v>8.204400000067834e-06</v>
       </c>
     </row>
     <row r="13">
@@ -962,7 +962,7 @@
         <v>0.6647471785545349</v>
       </c>
       <c r="K13" t="n">
-        <v>7.426300000588526e-06</v>
+        <v>8.35880000022371e-06</v>
       </c>
     </row>
     <row r="14">
@@ -1003,7 +1003,7 @@
         <v>0.6927752494812012</v>
       </c>
       <c r="K14" t="n">
-        <v>7.91879999997036e-06</v>
+        <v>9.714700000131416e-06</v>
       </c>
     </row>
     <row r="15">
@@ -1044,7 +1044,7 @@
         <v>0.6775802373886108</v>
       </c>
       <c r="K15" t="n">
-        <v>7.305999999516643e-06</v>
+        <v>8.330999999998311e-06</v>
       </c>
     </row>
     <row r="16">
@@ -1085,7 +1085,7 @@
         <v>0.6975191235542297</v>
       </c>
       <c r="K16" t="n">
-        <v>6.926300000486663e-06</v>
+        <v>8.282499999950232e-06</v>
       </c>
     </row>
     <row r="17">
@@ -1126,7 +1126,7 @@
         <v>0.8259356021881104</v>
       </c>
       <c r="K17" t="n">
-        <v>1.514829999905487e-05</v>
+        <v>1.829450000013821e-05</v>
       </c>
     </row>
     <row r="18">
@@ -1167,7 +1167,7 @@
         <v>0.7692122459411621</v>
       </c>
       <c r="K18" t="n">
-        <v>1.383190000160539e-05</v>
+        <v>1.489059999994424e-05</v>
       </c>
     </row>
     <row r="19">
@@ -1208,7 +1208,7 @@
         <v>0.7609123587608337</v>
       </c>
       <c r="K19" t="n">
-        <v>1.58119000006991e-05</v>
+        <v>1.664919999984704e-05</v>
       </c>
     </row>
     <row r="20">
@@ -1249,7 +1249,7 @@
         <v>0.8261111378669739</v>
       </c>
       <c r="K20" t="n">
-        <v>1.396920000115642e-05</v>
+        <v>1.749289999997927e-05</v>
       </c>
     </row>
     <row r="21">
@@ -1290,7 +1290,7 @@
         <v>0.7763814330101013</v>
       </c>
       <c r="K21" t="n">
-        <v>1.828459999887855e-05</v>
+        <v>1.499909999984084e-05</v>
       </c>
     </row>
     <row r="22">
@@ -1331,7 +1331,7 @@
         <v>0.6375079751014709</v>
       </c>
       <c r="K22" t="n">
-        <v>1.401409999925818e-05</v>
+        <v>1.478039999983594e-05</v>
       </c>
     </row>
     <row r="23">
@@ -1372,7 +1372,7 @@
         <v>0.6591068506240845</v>
       </c>
       <c r="K23" t="n">
-        <v>1.420580000012706e-05</v>
+        <v>1.528399999961039e-05</v>
       </c>
     </row>
     <row r="24">
@@ -1413,7 +1413,7 @@
         <v>0.6344265937805176</v>
       </c>
       <c r="K24" t="n">
-        <v>1.398140000128478e-05</v>
+        <v>1.498039999978573e-05</v>
       </c>
     </row>
     <row r="25">
@@ -1454,7 +1454,7 @@
         <v>0.7032672762870789</v>
       </c>
       <c r="K25" t="n">
-        <v>1.371109999854525e-05</v>
+        <v>1.562310000008438e-05</v>
       </c>
     </row>
     <row r="26">
@@ -1495,7 +1495,7 @@
         <v>0.7030646800994873</v>
       </c>
       <c r="K26" t="n">
-        <v>1.401950000035868e-05</v>
+        <v>1.521370000000388e-05</v>
       </c>
     </row>
   </sheetData>

--- a/162.xlsx
+++ b/162.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,20 +486,20 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-37.51 (1.15)</t>
+          <t>-37.51</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.96596360206604</v>
+        <v>0.3944210809469223</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1042959839105606</v>
+        <v>0.1042959878221154</v>
       </c>
       <c r="F2" t="n">
-        <v>17.98447036743164</v>
+        <v>14.84237528991699</v>
       </c>
       <c r="G2" t="n">
-        <v>0.08318112045526505</v>
+        <v>0.08318112520128489</v>
       </c>
       <c r="H2" t="n">
         <v>0.1949195116758347</v>
@@ -511,7 +511,7 @@
         <v>1.899414658546448</v>
       </c>
       <c r="K2" t="n">
-        <v>1.346120000016526e-05</v>
+        <v>2.832179999995788e-05</v>
       </c>
     </row>
     <row r="3">
@@ -527,20 +527,20 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-37.68 (1.19)</t>
+          <t>-37.68</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.678837776184082</v>
+        <v>0.3716653314828873</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1049587205052376</v>
+        <v>0.1049587244093418</v>
       </c>
       <c r="F3" t="n">
-        <v>14.37751388549805</v>
+        <v>12.70117623138428</v>
       </c>
       <c r="G3" t="n">
-        <v>0.08636249601840973</v>
+        <v>0.08636248918622733</v>
       </c>
       <c r="H3" t="n">
         <v>1.028795123100281</v>
@@ -552,7 +552,7 @@
         <v>2.021719694137573</v>
       </c>
       <c r="K3" t="n">
-        <v>8.164099999703468e-06</v>
+        <v>2.539040000010573e-05</v>
       </c>
     </row>
     <row r="4">
@@ -568,20 +568,20 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-40.97 (0.80)</t>
+          <t>-40.97</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.572483062744141</v>
+        <v>0.5610360656678677</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1328157484531403</v>
+        <v>0.1328157481104136</v>
       </c>
       <c r="F4" t="n">
-        <v>19.05227470397949</v>
+        <v>18.21930086326599</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1076611801981926</v>
+        <v>0.1076611945927143</v>
       </c>
       <c r="H4" t="n">
         <v>0.9844127893447876</v>
@@ -593,7 +593,7 @@
         <v>2.23393440246582</v>
       </c>
       <c r="K4" t="n">
-        <v>8.393999999952938e-06</v>
+        <v>3.292639999995117e-05</v>
       </c>
     </row>
     <row r="5">
@@ -609,20 +609,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-36.80 (1.28)</t>
+          <t>-36.80</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.9875187873840332</v>
+        <v>0.3960043675899506</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1032232865691185</v>
+        <v>0.1032232804819942</v>
       </c>
       <c r="F5" t="n">
-        <v>17.244873046875</v>
+        <v>14.88078626251221</v>
       </c>
       <c r="G5" t="n">
-        <v>0.07777422666549683</v>
+        <v>0.07777422753721476</v>
       </c>
       <c r="H5" t="n">
         <v>1.018619418144226</v>
@@ -634,7 +634,7 @@
         <v>1.836353302001953</v>
       </c>
       <c r="K5" t="n">
-        <v>7.823599999937869e-06</v>
+        <v>6.982179999999971e-05</v>
       </c>
     </row>
     <row r="6">
@@ -650,20 +650,20 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-42.86 (0.68)</t>
+          <t>-42.86</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.9971363544464111</v>
+        <v>0.651809765458107</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1827750653028488</v>
+        <v>0.1827750724107027</v>
       </c>
       <c r="F6" t="n">
-        <v>24.74639129638672</v>
+        <v>21.4876535949707</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1106208264827728</v>
+        <v>0.1106208183020353</v>
       </c>
       <c r="H6" t="n">
         <v>0.6961851119995117</v>
@@ -675,7 +675,7 @@
         <v>2.534233093261719</v>
       </c>
       <c r="K6" t="n">
-        <v>8.343599999989237e-06</v>
+        <v>2.371370000014394e-05</v>
       </c>
     </row>
     <row r="7">
@@ -691,20 +691,20 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-32.15 (1.03)</t>
+          <t>-32.15</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>86.03678894042969</v>
+        <v>85.50308422851562</v>
       </c>
       <c r="E7" t="n">
-        <v>4.745238304138184</v>
+        <v>4.745238411903381</v>
       </c>
       <c r="F7" t="n">
-        <v>7468.8974609375</v>
+        <v>7397.843859863281</v>
       </c>
       <c r="G7" t="n">
-        <v>20.0107364654541</v>
+        <v>20.01073612976074</v>
       </c>
       <c r="H7" t="n">
         <v>0.7199040651321411</v>
@@ -716,7 +716,7 @@
         <v>0.6462885141372681</v>
       </c>
       <c r="K7" t="n">
-        <v>8.053900000049906e-06</v>
+        <v>2.071630000000368e-05</v>
       </c>
     </row>
     <row r="8">
@@ -732,20 +732,20 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-31.94 (1.04)</t>
+          <t>-31.94</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>84.78179168701172</v>
+        <v>84.20316628265381</v>
       </c>
       <c r="E8" t="n">
-        <v>4.714409351348877</v>
+        <v>4.714409293651581</v>
       </c>
       <c r="F8" t="n">
-        <v>7239.12109375</v>
+        <v>7146.787145996093</v>
       </c>
       <c r="G8" t="n">
-        <v>19.62985992431641</v>
+        <v>19.62985975265503</v>
       </c>
       <c r="H8" t="n">
         <v>0.7220360636711121</v>
@@ -757,7 +757,7 @@
         <v>0.6290862560272217</v>
       </c>
       <c r="K8" t="n">
-        <v>1.021799999989526e-05</v>
+        <v>2.431589999991956e-05</v>
       </c>
     </row>
     <row r="9">
@@ -773,20 +773,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-32.20 (0.97)</t>
+          <t>-32.20</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>85.07386779785156</v>
+        <v>84.27514916229248</v>
       </c>
       <c r="E9" t="n">
-        <v>4.738084316253662</v>
+        <v>4.738084337234497</v>
       </c>
       <c r="F9" t="n">
-        <v>7324.83154296875</v>
+        <v>7202.296458496094</v>
       </c>
       <c r="G9" t="n">
-        <v>20.05002784729004</v>
+        <v>20.05002739143372</v>
       </c>
       <c r="H9" t="n">
         <v>0.7181195020675659</v>
@@ -798,7 +798,7 @@
         <v>0.6569992899894714</v>
       </c>
       <c r="K9" t="n">
-        <v>7.827399999769113e-06</v>
+        <v>2.004959999999301e-05</v>
       </c>
     </row>
     <row r="10">
@@ -814,20 +814,20 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-32.07 (0.90)</t>
+          <t>-32.07</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>85.20194244384766</v>
+        <v>84.68730562591553</v>
       </c>
       <c r="E10" t="n">
-        <v>4.759157657623291</v>
+        <v>4.759157948970794</v>
       </c>
       <c r="F10" t="n">
-        <v>7317.763671875</v>
+        <v>7230.858865722656</v>
       </c>
       <c r="G10" t="n">
-        <v>19.7773494720459</v>
+        <v>19.77734749412537</v>
       </c>
       <c r="H10" t="n">
         <v>0.7185947895050049</v>
@@ -839,7 +839,7 @@
         <v>0.6297457814216614</v>
       </c>
       <c r="K10" t="n">
-        <v>8.007699999780015e-06</v>
+        <v>1.875799999993433e-05</v>
       </c>
     </row>
     <row r="11">
@@ -855,20 +855,20 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-32.13 (0.77)</t>
+          <t>-32.13</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>86.17000579833984</v>
+        <v>84.62268690490723</v>
       </c>
       <c r="E11" t="n">
-        <v>4.747989177703857</v>
+        <v>4.747989253520966</v>
       </c>
       <c r="F11" t="n">
-        <v>7406.83642578125</v>
+        <v>7175.824537109375</v>
       </c>
       <c r="G11" t="n">
-        <v>19.70671272277832</v>
+        <v>19.70671310997009</v>
       </c>
       <c r="H11" t="n">
         <v>0.7172663807868958</v>
@@ -880,7 +880,7 @@
         <v>0.612906277179718</v>
       </c>
       <c r="K11" t="n">
-        <v>1.599919999989652e-05</v>
+        <v>3.39429000000564e-05</v>
       </c>
     </row>
     <row r="12">
@@ -896,20 +896,20 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-34.47 (1.27)</t>
+          <t>-34.47</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>84.92249298095703</v>
+        <v>83.69000473022462</v>
       </c>
       <c r="E12" t="n">
-        <v>4.717652797698975</v>
+        <v>4.7176529712677</v>
       </c>
       <c r="F12" t="n">
-        <v>7239.9765625</v>
+        <v>7044.419167480469</v>
       </c>
       <c r="G12" t="n">
-        <v>19.02021598815918</v>
+        <v>19.02021579933167</v>
       </c>
       <c r="H12" t="n">
         <v>0.7194445133209229</v>
@@ -921,7 +921,7 @@
         <v>0.6798930764198303</v>
       </c>
       <c r="K12" t="n">
-        <v>8.204400000067834e-06</v>
+        <v>2.114160000019183e-05</v>
       </c>
     </row>
     <row r="13">
@@ -937,20 +937,20 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-34.42 (1.33)</t>
+          <t>-34.42</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>84.17276763916016</v>
+        <v>83.19149970245361</v>
       </c>
       <c r="E13" t="n">
-        <v>4.710550308227539</v>
+        <v>4.710550173282623</v>
       </c>
       <c r="F13" t="n">
-        <v>7076.40576171875</v>
+        <v>6934.759482421875</v>
       </c>
       <c r="G13" t="n">
-        <v>19.0302562713623</v>
+        <v>19.03025841903687</v>
       </c>
       <c r="H13" t="n">
         <v>0.718348503112793</v>
@@ -962,7 +962,7 @@
         <v>0.6647471785545349</v>
       </c>
       <c r="K13" t="n">
-        <v>8.35880000022371e-06</v>
+        <v>2.336209999998573e-05</v>
       </c>
     </row>
     <row r="14">
@@ -978,20 +978,20 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-34.32 (1.07)</t>
+          <t>-34.32</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>81.89128875732422</v>
+        <v>81.19187330627442</v>
       </c>
       <c r="E14" t="n">
-        <v>4.687593936920166</v>
+        <v>4.687594055652618</v>
       </c>
       <c r="F14" t="n">
-        <v>6755.34130859375</v>
+        <v>6653.133884277344</v>
       </c>
       <c r="G14" t="n">
-        <v>18.75619888305664</v>
+        <v>18.75619852638244</v>
       </c>
       <c r="H14" t="n">
         <v>0.7167642116546631</v>
@@ -1003,7 +1003,7 @@
         <v>0.6927752494812012</v>
       </c>
       <c r="K14" t="n">
-        <v>9.714700000131416e-06</v>
+        <v>2.251610000007531e-05</v>
       </c>
     </row>
     <row r="15">
@@ -1019,20 +1019,20 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-34.46 (1.29)</t>
+          <t>-34.46</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>85.08256530761719</v>
+        <v>84.19227960968017</v>
       </c>
       <c r="E15" t="n">
-        <v>4.69942569732666</v>
+        <v>4.699425678730011</v>
       </c>
       <c r="F15" t="n">
-        <v>7261.630859375</v>
+        <v>7129.119458007813</v>
       </c>
       <c r="G15" t="n">
-        <v>19.18807029724121</v>
+        <v>19.18807070350647</v>
       </c>
       <c r="H15" t="n">
         <v>0.7159428000450134</v>
@@ -1044,7 +1044,7 @@
         <v>0.6775802373886108</v>
       </c>
       <c r="K15" t="n">
-        <v>8.330999999998311e-06</v>
+        <v>2.209419999985584e-05</v>
       </c>
     </row>
     <row r="16">
@@ -1060,20 +1060,20 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-34.47 (1.28)</t>
+          <t>-34.47</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>84.13075256347656</v>
+        <v>83.32168952941895</v>
       </c>
       <c r="E16" t="n">
-        <v>4.703958511352539</v>
+        <v>4.703958561420441</v>
       </c>
       <c r="F16" t="n">
-        <v>7166.01904296875</v>
+        <v>7018.469251953125</v>
       </c>
       <c r="G16" t="n">
-        <v>19.135009765625</v>
+        <v>19.13500893974304</v>
       </c>
       <c r="H16" t="n">
         <v>0.7165584564208984</v>
@@ -1085,7 +1085,7 @@
         <v>0.6975191235542297</v>
       </c>
       <c r="K16" t="n">
-        <v>8.282499999950232e-06</v>
+        <v>2.007819999994354e-05</v>
       </c>
     </row>
     <row r="17">
@@ -1101,20 +1101,20 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-34.49 (1.42)</t>
+          <t>-34.49</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.5952963829040527</v>
+        <v>0.2466912651956081</v>
       </c>
       <c r="E17" t="n">
-        <v>0.04840697348117828</v>
+        <v>0.04840697149932385</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6512069702148438</v>
+        <v>0.1889150236845016</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0003086223441641778</v>
+        <v>0.0003086223388163489</v>
       </c>
       <c r="H17" t="n">
         <v>0.07230685651302338</v>
@@ -1126,7 +1126,7 @@
         <v>0.8259356021881104</v>
       </c>
       <c r="K17" t="n">
-        <v>1.829450000013821e-05</v>
+        <v>4.352820000008251e-05</v>
       </c>
     </row>
     <row r="18">
@@ -1142,20 +1142,20 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-34.17 (0.46)</t>
+          <t>-34.17</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.6545140147209167</v>
+        <v>0.4181239830553531</v>
       </c>
       <c r="E18" t="n">
-        <v>0.05324654653668404</v>
+        <v>0.05324654508009553</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8201408386230469</v>
+        <v>0.6792677726745605</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0007568926666863263</v>
+        <v>0.0007568926456442568</v>
       </c>
       <c r="H18" t="n">
         <v>0.06854981184005737</v>
@@ -1167,7 +1167,7 @@
         <v>0.7692122459411621</v>
       </c>
       <c r="K18" t="n">
-        <v>1.489059999994424e-05</v>
+        <v>5.479360000003908e-05</v>
       </c>
     </row>
     <row r="19">
@@ -1183,20 +1183,20 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-34.40 (1.11)</t>
+          <t>-34.40</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.5810646414756775</v>
+        <v>0.2621413843035698</v>
       </c>
       <c r="E19" t="n">
-        <v>0.04941532015800476</v>
+        <v>0.04941532082855701</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6877403259277344</v>
+        <v>0.4422568576335907</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0007793494150973856</v>
+        <v>0.0007793494511279278</v>
       </c>
       <c r="H19" t="n">
         <v>0.06968240439891815</v>
@@ -1208,7 +1208,7 @@
         <v>0.7609123587608337</v>
       </c>
       <c r="K19" t="n">
-        <v>1.664919999984704e-05</v>
+        <v>3.992599999992308e-05</v>
       </c>
     </row>
     <row r="20">
@@ -1224,20 +1224,20 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-34.99 (1.35)</t>
+          <t>-34.99</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.6882423758506775</v>
+        <v>0.2952102217525244</v>
       </c>
       <c r="E20" t="n">
-        <v>0.04976234585046768</v>
+        <v>0.04976234791055321</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4388465881347656</v>
+        <v>0.1777613739967346</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0002122677688021213</v>
+        <v>0.00021226779439246</v>
       </c>
       <c r="H20" t="n">
         <v>0.0725826621055603</v>
@@ -1249,7 +1249,7 @@
         <v>0.8261111378669739</v>
       </c>
       <c r="K20" t="n">
-        <v>1.749289999997927e-05</v>
+        <v>4.171459999997751e-05</v>
       </c>
     </row>
     <row r="21">
@@ -1265,20 +1265,20 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-34.41 (0.34)</t>
+          <t>-34.41</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.6090268492698669</v>
+        <v>0.2937943091094494</v>
       </c>
       <c r="E21" t="n">
-        <v>0.05173289030790329</v>
+        <v>0.05173289460688829</v>
       </c>
       <c r="F21" t="n">
-        <v>0.88250732421875</v>
+        <v>0.6190450744628906</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0005299569456838071</v>
+        <v>0.0005299569150665775</v>
       </c>
       <c r="H21" t="n">
         <v>0.06969688087701797</v>
@@ -1290,7 +1290,7 @@
         <v>0.7763814330101013</v>
       </c>
       <c r="K21" t="n">
-        <v>1.499909999984084e-05</v>
+        <v>4.2783800000052e-05</v>
       </c>
     </row>
     <row r="22">
@@ -1306,20 +1306,20 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-8.20 (0.08)</t>
+          <t>-8.20</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1.432988882064819</v>
+        <v>0.6064836847782135</v>
       </c>
       <c r="E22" t="n">
-        <v>0.04169116169214249</v>
+        <v>0.04169116235151887</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3640086650848389</v>
+        <v>0.08561419242620469</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0001154186757048592</v>
+        <v>0.0001154186749081418</v>
       </c>
       <c r="H22" t="n">
         <v>0.04552223905920982</v>
@@ -1331,7 +1331,7 @@
         <v>0.6375079751014709</v>
       </c>
       <c r="K22" t="n">
-        <v>1.478039999983594e-05</v>
+        <v>3.336550000017269e-05</v>
       </c>
     </row>
     <row r="23">
@@ -1347,20 +1347,20 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-7.00 (0.06)</t>
+          <t>-7.00</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1.532139778137207</v>
+        <v>1.030174807071686</v>
       </c>
       <c r="E23" t="n">
-        <v>0.04291481897234917</v>
+        <v>0.04291481583192944</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4306063652038574</v>
+        <v>0.09767026370763779</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0001140713502536528</v>
+        <v>0.0001140713521162979</v>
       </c>
       <c r="H23" t="n">
         <v>0.05051264539361</v>
@@ -1372,7 +1372,7 @@
         <v>0.6591068506240845</v>
       </c>
       <c r="K23" t="n">
-        <v>1.528399999961039e-05</v>
+        <v>3.369389999988925e-05</v>
       </c>
     </row>
     <row r="24">
@@ -1388,20 +1388,20 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-7.62 (0.19)</t>
+          <t>-7.62</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1.460663795471191</v>
+        <v>0.686611274600029</v>
       </c>
       <c r="E24" t="n">
-        <v>0.04401947557926178</v>
+        <v>0.04401947408914566</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1893651485443115</v>
+        <v>0.03567489624023437</v>
       </c>
       <c r="G24" t="n">
-        <v>4.119665391044691e-05</v>
+        <v>4.119664989411831e-05</v>
       </c>
       <c r="H24" t="n">
         <v>0.05103453621268272</v>
@@ -1413,7 +1413,7 @@
         <v>0.6344265937805176</v>
       </c>
       <c r="K24" t="n">
-        <v>1.498039999978573e-05</v>
+        <v>4.146549999995841e-05</v>
       </c>
     </row>
     <row r="25">
@@ -1429,20 +1429,20 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-6.24 (0.30)</t>
+          <t>-6.24</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1.564711093902588</v>
+        <v>0.6505242031216621</v>
       </c>
       <c r="E25" t="n">
-        <v>0.04108690842986107</v>
+        <v>0.04108691008761525</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2898274660110474</v>
+        <v>0.0518247749209404</v>
       </c>
       <c r="G25" t="n">
-        <v>6.130744441179559e-05</v>
+        <v>6.130743998983234e-05</v>
       </c>
       <c r="H25" t="n">
         <v>0.04903533309698105</v>
@@ -1454,7 +1454,7 @@
         <v>0.7032672762870789</v>
       </c>
       <c r="K25" t="n">
-        <v>1.562310000008438e-05</v>
+        <v>4.124260000003233e-05</v>
       </c>
     </row>
     <row r="26">
@@ -1470,20 +1470,20 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-8.77 (0.09)</t>
+          <t>-8.77</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1.395487308502197</v>
+        <v>0.7081052532196045</v>
       </c>
       <c r="E26" t="n">
-        <v>0.04439558088779449</v>
+        <v>0.04439557975158095</v>
       </c>
       <c r="F26" t="n">
-        <v>0.370948314666748</v>
+        <v>0.05564244824647904</v>
       </c>
       <c r="G26" t="n">
-        <v>5.735258673666976e-05</v>
+        <v>5.735258352797246e-05</v>
       </c>
       <c r="H26" t="n">
         <v>0.05177820101380348</v>
@@ -1495,7 +1495,212 @@
         <v>0.7030646800994873</v>
       </c>
       <c r="K26" t="n">
-        <v>1.521370000000388e-05</v>
+        <v>3.653540000004796e-05</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Ablated PINN</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Run 1</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>-43.67</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>0.5509438116550446</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.1138138962313533</v>
+      </c>
+      <c r="F27" t="n">
+        <v>16.06996207809448</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.159273573577404</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.9768306612968445</v>
+      </c>
+      <c r="I27" t="n">
+        <v>2.688024997711182</v>
+      </c>
+      <c r="J27" t="n">
+        <v>3.303707122802734</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1.574040000014065e-05</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Ablated PINN</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Run 2</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>-48.33</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>0.5882579138278962</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.08680037485063076</v>
+      </c>
+      <c r="F28" t="n">
+        <v>15.59637615776062</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.1470350993275642</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1.045491933822632</v>
+      </c>
+      <c r="I28" t="n">
+        <v>3.194693088531494</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2.807586193084717</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2.773260000003574e-05</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Ablated PINN</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Run 3</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>-48.10</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>0.5766609728336334</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.08606121307611465</v>
+      </c>
+      <c r="F29" t="n">
+        <v>15.22148032188415</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.1455959653407335</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1.044873833656311</v>
+      </c>
+      <c r="I29" t="n">
+        <v>3.167407274246216</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2.807583093643188</v>
+      </c>
+      <c r="K29" t="n">
+        <v>6.22636999999031e-05</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Ablated PINN</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Run 4</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>-45.40</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>0.5920081272125244</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.1056748838499188</v>
+      </c>
+      <c r="F30" t="n">
+        <v>18.46376594161987</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.1584535791426897</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.4691900610923767</v>
+      </c>
+      <c r="I30" t="n">
+        <v>2.936410188674927</v>
+      </c>
+      <c r="J30" t="n">
+        <v>3.118694067001343</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1.552960000003623e-05</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Ablated PINN</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Run 5</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>-48.50</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>0.379934819817543</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.09046404175460339</v>
+      </c>
+      <c r="F31" t="n">
+        <v>15.3356696395874</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.1412137556821108</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1.041359066963196</v>
+      </c>
+      <c r="I31" t="n">
+        <v>3.185632228851318</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2.804337978363037</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1.590480000004391e-05</v>
       </c>
     </row>
   </sheetData>

--- a/162.xlsx
+++ b/162.xlsx
@@ -486,20 +486,20 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-37.51</t>
+          <t>-37.51 (1.15)</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.3944210809469223</v>
+        <v>0.96596360206604</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1042959878221154</v>
+        <v>0.1042959839105606</v>
       </c>
       <c r="F2" t="n">
-        <v>14.84237528991699</v>
+        <v>17.98447036743164</v>
       </c>
       <c r="G2" t="n">
-        <v>0.08318112520128489</v>
+        <v>0.08318112045526505</v>
       </c>
       <c r="H2" t="n">
         <v>0.1949195116758347</v>
@@ -511,7 +511,7 @@
         <v>1.899414658546448</v>
       </c>
       <c r="K2" t="n">
-        <v>2.832179999995788e-05</v>
+        <v>1.509359999909066e-05</v>
       </c>
     </row>
     <row r="3">
@@ -527,20 +527,20 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-37.68</t>
+          <t>-37.68 (1.19)</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.3716653314828873</v>
+        <v>0.678837776184082</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1049587244093418</v>
+        <v>0.1049587205052376</v>
       </c>
       <c r="F3" t="n">
-        <v>12.70117623138428</v>
+        <v>14.37751388549805</v>
       </c>
       <c r="G3" t="n">
-        <v>0.08636248918622733</v>
+        <v>0.08636249601840973</v>
       </c>
       <c r="H3" t="n">
         <v>1.028795123100281</v>
@@ -552,7 +552,7 @@
         <v>2.021719694137573</v>
       </c>
       <c r="K3" t="n">
-        <v>2.539040000010573e-05</v>
+        <v>7.879100005084184e-06</v>
       </c>
     </row>
     <row r="4">
@@ -568,20 +568,20 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-40.97</t>
+          <t>-40.97 (0.80)</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.5610360656678677</v>
+        <v>1.572483062744141</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1328157481104136</v>
+        <v>0.1328157484531403</v>
       </c>
       <c r="F4" t="n">
-        <v>18.21930086326599</v>
+        <v>19.05227470397949</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1076611945927143</v>
+        <v>0.1076611801981926</v>
       </c>
       <c r="H4" t="n">
         <v>0.9844127893447876</v>
@@ -593,7 +593,7 @@
         <v>2.23393440246582</v>
       </c>
       <c r="K4" t="n">
-        <v>3.292639999995117e-05</v>
+        <v>8.027399999264163e-06</v>
       </c>
     </row>
     <row r="5">
@@ -609,20 +609,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-36.80</t>
+          <t>-36.80 (1.28)</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.3960043675899506</v>
+        <v>0.9875187873840332</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1032232804819942</v>
+        <v>0.1032232865691185</v>
       </c>
       <c r="F5" t="n">
-        <v>14.88078626251221</v>
+        <v>17.244873046875</v>
       </c>
       <c r="G5" t="n">
-        <v>0.07777422753721476</v>
+        <v>0.07777422666549683</v>
       </c>
       <c r="H5" t="n">
         <v>1.018619418144226</v>
@@ -634,7 +634,7 @@
         <v>1.836353302001953</v>
       </c>
       <c r="K5" t="n">
-        <v>6.982179999999971e-05</v>
+        <v>9.801599997445009e-06</v>
       </c>
     </row>
     <row r="6">
@@ -650,20 +650,20 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-42.86</t>
+          <t>-42.86 (0.68)</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.651809765458107</v>
+        <v>0.9971363544464111</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1827750724107027</v>
+        <v>0.1827750653028488</v>
       </c>
       <c r="F6" t="n">
-        <v>21.4876535949707</v>
+        <v>24.74639129638672</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1106208183020353</v>
+        <v>0.1106208264827728</v>
       </c>
       <c r="H6" t="n">
         <v>0.6961851119995117</v>
@@ -675,7 +675,7 @@
         <v>2.534233093261719</v>
       </c>
       <c r="K6" t="n">
-        <v>2.371370000014394e-05</v>
+        <v>8.075999998254701e-06</v>
       </c>
     </row>
     <row r="7">
@@ -691,20 +691,20 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-32.15</t>
+          <t>-32.15 (1.03)</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>85.50308422851562</v>
+        <v>86.03678894042969</v>
       </c>
       <c r="E7" t="n">
-        <v>4.745238411903381</v>
+        <v>4.745238304138184</v>
       </c>
       <c r="F7" t="n">
-        <v>7397.843859863281</v>
+        <v>7468.8974609375</v>
       </c>
       <c r="G7" t="n">
-        <v>20.01073612976074</v>
+        <v>20.0107364654541</v>
       </c>
       <c r="H7" t="n">
         <v>0.7199040651321411</v>
@@ -716,7 +716,7 @@
         <v>0.6462885141372681</v>
       </c>
       <c r="K7" t="n">
-        <v>2.071630000000368e-05</v>
+        <v>8.102299994789064e-06</v>
       </c>
     </row>
     <row r="8">
@@ -732,20 +732,20 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-31.94</t>
+          <t>-31.94 (1.04)</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>84.20316628265381</v>
+        <v>84.78179168701172</v>
       </c>
       <c r="E8" t="n">
-        <v>4.714409293651581</v>
+        <v>4.714409351348877</v>
       </c>
       <c r="F8" t="n">
-        <v>7146.787145996093</v>
+        <v>7239.12109375</v>
       </c>
       <c r="G8" t="n">
-        <v>19.62985975265503</v>
+        <v>19.62985992431641</v>
       </c>
       <c r="H8" t="n">
         <v>0.7220360636711121</v>
@@ -757,7 +757,7 @@
         <v>0.6290862560272217</v>
       </c>
       <c r="K8" t="n">
-        <v>2.431589999991956e-05</v>
+        <v>7.820099999662489e-06</v>
       </c>
     </row>
     <row r="9">
@@ -773,20 +773,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-32.20</t>
+          <t>-32.20 (0.97)</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>84.27514916229248</v>
+        <v>85.07386779785156</v>
       </c>
       <c r="E9" t="n">
-        <v>4.738084337234497</v>
+        <v>4.738084316253662</v>
       </c>
       <c r="F9" t="n">
-        <v>7202.296458496094</v>
+        <v>7324.83154296875</v>
       </c>
       <c r="G9" t="n">
-        <v>20.05002739143372</v>
+        <v>20.05002784729004</v>
       </c>
       <c r="H9" t="n">
         <v>0.7181195020675659</v>
@@ -798,7 +798,7 @@
         <v>0.6569992899894714</v>
       </c>
       <c r="K9" t="n">
-        <v>2.004959999999301e-05</v>
+        <v>8.319599997776095e-06</v>
       </c>
     </row>
     <row r="10">
@@ -814,20 +814,20 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-32.07</t>
+          <t>-32.07 (0.90)</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>84.68730562591553</v>
+        <v>85.20194244384766</v>
       </c>
       <c r="E10" t="n">
-        <v>4.759157948970794</v>
+        <v>4.759157657623291</v>
       </c>
       <c r="F10" t="n">
-        <v>7230.858865722656</v>
+        <v>7317.763671875</v>
       </c>
       <c r="G10" t="n">
-        <v>19.77734749412537</v>
+        <v>19.7773494720459</v>
       </c>
       <c r="H10" t="n">
         <v>0.7185947895050049</v>
@@ -839,7 +839,7 @@
         <v>0.6297457814216614</v>
       </c>
       <c r="K10" t="n">
-        <v>1.875799999993433e-05</v>
+        <v>8.177600000635721e-06</v>
       </c>
     </row>
     <row r="11">
@@ -855,20 +855,20 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-32.13</t>
+          <t>-32.13 (0.77)</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>84.62268690490723</v>
+        <v>86.17000579833984</v>
       </c>
       <c r="E11" t="n">
-        <v>4.747989253520966</v>
+        <v>4.747989177703857</v>
       </c>
       <c r="F11" t="n">
-        <v>7175.824537109375</v>
+        <v>7406.83642578125</v>
       </c>
       <c r="G11" t="n">
-        <v>19.70671310997009</v>
+        <v>19.70671272277832</v>
       </c>
       <c r="H11" t="n">
         <v>0.7172663807868958</v>
@@ -880,7 +880,7 @@
         <v>0.612906277179718</v>
       </c>
       <c r="K11" t="n">
-        <v>3.39429000000564e-05</v>
+        <v>8.327199997438583e-06</v>
       </c>
     </row>
     <row r="12">
@@ -896,20 +896,20 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-34.47</t>
+          <t>-34.47 (1.27)</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>83.69000473022462</v>
+        <v>84.92249298095703</v>
       </c>
       <c r="E12" t="n">
-        <v>4.7176529712677</v>
+        <v>4.717652797698975</v>
       </c>
       <c r="F12" t="n">
-        <v>7044.419167480469</v>
+        <v>7239.9765625</v>
       </c>
       <c r="G12" t="n">
-        <v>19.02021579933167</v>
+        <v>19.02021598815918</v>
       </c>
       <c r="H12" t="n">
         <v>0.7194445133209229</v>
@@ -921,7 +921,7 @@
         <v>0.6798930764198303</v>
       </c>
       <c r="K12" t="n">
-        <v>2.114160000019183e-05</v>
+        <v>8.340800006408245e-06</v>
       </c>
     </row>
     <row r="13">
@@ -937,20 +937,20 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-34.42</t>
+          <t>-34.42 (1.33)</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>83.19149970245361</v>
+        <v>84.17276763916016</v>
       </c>
       <c r="E13" t="n">
-        <v>4.710550173282623</v>
+        <v>4.710550308227539</v>
       </c>
       <c r="F13" t="n">
-        <v>6934.759482421875</v>
+        <v>7076.40576171875</v>
       </c>
       <c r="G13" t="n">
-        <v>19.03025841903687</v>
+        <v>19.0302562713623</v>
       </c>
       <c r="H13" t="n">
         <v>0.718348503112793</v>
@@ -962,7 +962,7 @@
         <v>0.6647471785545349</v>
       </c>
       <c r="K13" t="n">
-        <v>2.336209999998573e-05</v>
+        <v>8.432599999650847e-06</v>
       </c>
     </row>
     <row r="14">
@@ -978,20 +978,20 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-34.32</t>
+          <t>-34.32 (1.07)</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>81.19187330627442</v>
+        <v>81.89128875732422</v>
       </c>
       <c r="E14" t="n">
-        <v>4.687594055652618</v>
+        <v>4.687593936920166</v>
       </c>
       <c r="F14" t="n">
-        <v>6653.133884277344</v>
+        <v>6755.34130859375</v>
       </c>
       <c r="G14" t="n">
-        <v>18.75619852638244</v>
+        <v>18.75619888305664</v>
       </c>
       <c r="H14" t="n">
         <v>0.7167642116546631</v>
@@ -1003,7 +1003,7 @@
         <v>0.6927752494812012</v>
       </c>
       <c r="K14" t="n">
-        <v>2.251610000007531e-05</v>
+        <v>8.23149999632733e-06</v>
       </c>
     </row>
     <row r="15">
@@ -1019,20 +1019,20 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-34.46</t>
+          <t>-34.46 (1.29)</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>84.19227960968017</v>
+        <v>85.08256530761719</v>
       </c>
       <c r="E15" t="n">
-        <v>4.699425678730011</v>
+        <v>4.69942569732666</v>
       </c>
       <c r="F15" t="n">
-        <v>7129.119458007813</v>
+        <v>7261.630859375</v>
       </c>
       <c r="G15" t="n">
-        <v>19.18807070350647</v>
+        <v>19.18807029724121</v>
       </c>
       <c r="H15" t="n">
         <v>0.7159428000450134</v>
@@ -1044,7 +1044,7 @@
         <v>0.6775802373886108</v>
       </c>
       <c r="K15" t="n">
-        <v>2.209419999985584e-05</v>
+        <v>8.684100001119077e-06</v>
       </c>
     </row>
     <row r="16">
@@ -1060,20 +1060,20 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-34.47</t>
+          <t>-34.47 (1.28)</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>83.32168952941895</v>
+        <v>84.13075256347656</v>
       </c>
       <c r="E16" t="n">
-        <v>4.703958561420441</v>
+        <v>4.703958511352539</v>
       </c>
       <c r="F16" t="n">
-        <v>7018.469251953125</v>
+        <v>7166.01904296875</v>
       </c>
       <c r="G16" t="n">
-        <v>19.13500893974304</v>
+        <v>19.135009765625</v>
       </c>
       <c r="H16" t="n">
         <v>0.7165584564208984</v>
@@ -1085,7 +1085,7 @@
         <v>0.6975191235542297</v>
       </c>
       <c r="K16" t="n">
-        <v>2.007819999994354e-05</v>
+        <v>8.469300002616365e-06</v>
       </c>
     </row>
     <row r="17">
@@ -1101,20 +1101,20 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-34.49</t>
+          <t>-34.49 (1.42)</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.2466912651956081</v>
+        <v>0.5952963829040527</v>
       </c>
       <c r="E17" t="n">
-        <v>0.04840697149932385</v>
+        <v>0.04840697348117828</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1889150236845016</v>
+        <v>0.6512069702148438</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0003086223388163489</v>
+        <v>0.0003086223441641778</v>
       </c>
       <c r="H17" t="n">
         <v>0.07230685651302338</v>
@@ -1126,7 +1126,7 @@
         <v>0.8259356021881104</v>
       </c>
       <c r="K17" t="n">
-        <v>4.352820000008251e-05</v>
+        <v>1.723109999875305e-05</v>
       </c>
     </row>
     <row r="18">
@@ -1142,20 +1142,20 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-34.17</t>
+          <t>-34.17 (0.46)</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.4181239830553531</v>
+        <v>0.6545140147209167</v>
       </c>
       <c r="E18" t="n">
-        <v>0.05324654508009553</v>
+        <v>0.05324654653668404</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6792677726745605</v>
+        <v>0.8201408386230469</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0007568926456442568</v>
+        <v>0.0007568926666863263</v>
       </c>
       <c r="H18" t="n">
         <v>0.06854981184005737</v>
@@ -1167,7 +1167,7 @@
         <v>0.7692122459411621</v>
       </c>
       <c r="K18" t="n">
-        <v>5.479360000003908e-05</v>
+        <v>1.497709999966901e-05</v>
       </c>
     </row>
     <row r="19">
@@ -1183,20 +1183,20 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-34.40</t>
+          <t>-34.40 (1.11)</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.2621413843035698</v>
+        <v>0.5810646414756775</v>
       </c>
       <c r="E19" t="n">
-        <v>0.04941532082855701</v>
+        <v>0.04941532015800476</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4422568576335907</v>
+        <v>0.6877403259277344</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0007793494511279278</v>
+        <v>0.0007793494150973856</v>
       </c>
       <c r="H19" t="n">
         <v>0.06968240439891815</v>
@@ -1208,7 +1208,7 @@
         <v>0.7609123587608337</v>
       </c>
       <c r="K19" t="n">
-        <v>3.992599999992308e-05</v>
+        <v>1.547929999651387e-05</v>
       </c>
     </row>
     <row r="20">
@@ -1224,20 +1224,20 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-34.99</t>
+          <t>-34.99 (1.35)</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.2952102217525244</v>
+        <v>0.6882423758506775</v>
       </c>
       <c r="E20" t="n">
-        <v>0.04976234791055321</v>
+        <v>0.04976234585046768</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1777613739967346</v>
+        <v>0.4388465881347656</v>
       </c>
       <c r="G20" t="n">
-        <v>0.00021226779439246</v>
+        <v>0.0002122677688021213</v>
       </c>
       <c r="H20" t="n">
         <v>0.0725826621055603</v>
@@ -1249,7 +1249,7 @@
         <v>0.8261111378669739</v>
       </c>
       <c r="K20" t="n">
-        <v>4.171459999997751e-05</v>
+        <v>1.500880000094185e-05</v>
       </c>
     </row>
     <row r="21">
@@ -1265,20 +1265,20 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-34.41</t>
+          <t>-34.41 (0.34)</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.2937943091094494</v>
+        <v>0.6090268492698669</v>
       </c>
       <c r="E21" t="n">
-        <v>0.05173289460688829</v>
+        <v>0.05173289030790329</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6190450744628906</v>
+        <v>0.88250732421875</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0005299569150665775</v>
+        <v>0.0005299569456838071</v>
       </c>
       <c r="H21" t="n">
         <v>0.06969688087701797</v>
@@ -1290,7 +1290,7 @@
         <v>0.7763814330101013</v>
       </c>
       <c r="K21" t="n">
-        <v>4.2783800000052e-05</v>
+        <v>1.587709999876097e-05</v>
       </c>
     </row>
     <row r="22">
@@ -1306,20 +1306,20 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-8.20</t>
+          <t>-8.20 (0.08)</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.6064836847782135</v>
+        <v>1.432988882064819</v>
       </c>
       <c r="E22" t="n">
-        <v>0.04169116235151887</v>
+        <v>0.04169116169214249</v>
       </c>
       <c r="F22" t="n">
-        <v>0.08561419242620469</v>
+        <v>0.3640086650848389</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0001154186749081418</v>
+        <v>0.0001154186757048592</v>
       </c>
       <c r="H22" t="n">
         <v>0.04552223905920982</v>
@@ -1331,7 +1331,7 @@
         <v>0.6375079751014709</v>
       </c>
       <c r="K22" t="n">
-        <v>3.336550000017269e-05</v>
+        <v>1.472459999786224e-05</v>
       </c>
     </row>
     <row r="23">
@@ -1347,20 +1347,20 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-7.00</t>
+          <t>-7.00 (0.06)</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1.030174807071686</v>
+        <v>1.532139778137207</v>
       </c>
       <c r="E23" t="n">
-        <v>0.04291481583192944</v>
+        <v>0.04291481897234917</v>
       </c>
       <c r="F23" t="n">
-        <v>0.09767026370763779</v>
+        <v>0.4306063652038574</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0001140713521162979</v>
+        <v>0.0001140713502536528</v>
       </c>
       <c r="H23" t="n">
         <v>0.05051264539361</v>
@@ -1372,7 +1372,7 @@
         <v>0.6591068506240845</v>
       </c>
       <c r="K23" t="n">
-        <v>3.369389999988925e-05</v>
+        <v>1.569920000474667e-05</v>
       </c>
     </row>
     <row r="24">
@@ -1388,20 +1388,20 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-7.62</t>
+          <t>-7.62 (0.19)</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.686611274600029</v>
+        <v>1.460663795471191</v>
       </c>
       <c r="E24" t="n">
-        <v>0.04401947408914566</v>
+        <v>0.04401947557926178</v>
       </c>
       <c r="F24" t="n">
-        <v>0.03567489624023437</v>
+        <v>0.1893651485443115</v>
       </c>
       <c r="G24" t="n">
-        <v>4.119664989411831e-05</v>
+        <v>4.119665391044691e-05</v>
       </c>
       <c r="H24" t="n">
         <v>0.05103453621268272</v>
@@ -1413,7 +1413,7 @@
         <v>0.6344265937805176</v>
       </c>
       <c r="K24" t="n">
-        <v>4.146549999995841e-05</v>
+        <v>1.529560000199126e-05</v>
       </c>
     </row>
     <row r="25">
@@ -1429,20 +1429,20 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-6.24</t>
+          <t>-6.24 (0.30)</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.6505242031216621</v>
+        <v>1.564711093902588</v>
       </c>
       <c r="E25" t="n">
-        <v>0.04108691008761525</v>
+        <v>0.04108690842986107</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0518247749209404</v>
+        <v>0.2898274660110474</v>
       </c>
       <c r="G25" t="n">
-        <v>6.130743998983234e-05</v>
+        <v>6.130744441179559e-05</v>
       </c>
       <c r="H25" t="n">
         <v>0.04903533309698105</v>
@@ -1454,7 +1454,7 @@
         <v>0.7032672762870789</v>
       </c>
       <c r="K25" t="n">
-        <v>4.124260000003233e-05</v>
+        <v>1.457149999623653e-05</v>
       </c>
     </row>
     <row r="26">
@@ -1470,20 +1470,20 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-8.77</t>
+          <t>-8.77 (0.09)</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.7081052532196045</v>
+        <v>1.395487308502197</v>
       </c>
       <c r="E26" t="n">
-        <v>0.04439557975158095</v>
+        <v>0.04439558088779449</v>
       </c>
       <c r="F26" t="n">
-        <v>0.05564244824647904</v>
+        <v>0.370948314666748</v>
       </c>
       <c r="G26" t="n">
-        <v>5.735258352797246e-05</v>
+        <v>5.735258673666976e-05</v>
       </c>
       <c r="H26" t="n">
         <v>0.05177820101380348</v>
@@ -1495,7 +1495,7 @@
         <v>0.7030646800994873</v>
       </c>
       <c r="K26" t="n">
-        <v>3.653540000004796e-05</v>
+        <v>1.506720000179484e-05</v>
       </c>
     </row>
     <row r="27">
@@ -1511,20 +1511,20 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-43.67</t>
+          <t>-43.67 (0.98)</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.5509438116550446</v>
+        <v>0.9956388473510742</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1138138962313533</v>
+        <v>0.1138138994574547</v>
       </c>
       <c r="F27" t="n">
-        <v>16.06996207809448</v>
+        <v>17.18492126464844</v>
       </c>
       <c r="G27" t="n">
-        <v>0.159273573577404</v>
+        <v>0.1592735648155212</v>
       </c>
       <c r="H27" t="n">
         <v>0.9768306612968445</v>
@@ -1536,7 +1536,7 @@
         <v>3.303707122802734</v>
       </c>
       <c r="K27" t="n">
-        <v>1.574040000014065e-05</v>
+        <v>1.741729999775998e-05</v>
       </c>
     </row>
     <row r="28">
@@ -1552,20 +1552,20 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-48.33</t>
+          <t>-48.33 (1.14)</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.5882579138278962</v>
+        <v>0.6411409378051758</v>
       </c>
       <c r="E28" t="n">
-        <v>0.08680037485063076</v>
+        <v>0.08680037409067154</v>
       </c>
       <c r="F28" t="n">
-        <v>15.59637615776062</v>
+        <v>17.94316101074219</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1470350993275642</v>
+        <v>0.1470350921154022</v>
       </c>
       <c r="H28" t="n">
         <v>1.045491933822632</v>
@@ -1577,7 +1577,7 @@
         <v>2.807586193084717</v>
       </c>
       <c r="K28" t="n">
-        <v>2.773260000003574e-05</v>
+        <v>8.950399998866487e-06</v>
       </c>
     </row>
     <row r="29">
@@ -1593,20 +1593,20 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>-48.10</t>
+          <t>-48.10 (1.04)</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.5766609728336334</v>
+        <v>0.8933286666870117</v>
       </c>
       <c r="E29" t="n">
-        <v>0.08606121307611465</v>
+        <v>0.08606120944023132</v>
       </c>
       <c r="F29" t="n">
-        <v>15.22148032188415</v>
+        <v>17.45991706848145</v>
       </c>
       <c r="G29" t="n">
-        <v>0.1455959653407335</v>
+        <v>0.1455959677696228</v>
       </c>
       <c r="H29" t="n">
         <v>1.044873833656311</v>
@@ -1618,7 +1618,7 @@
         <v>2.807583093643188</v>
       </c>
       <c r="K29" t="n">
-        <v>6.22636999999031e-05</v>
+        <v>7.887599997047801e-06</v>
       </c>
     </row>
     <row r="30">
@@ -1634,20 +1634,20 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>-45.40</t>
+          <t>-45.40 (1.14)</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.5920081272125244</v>
+        <v>0.8894774913787842</v>
       </c>
       <c r="E30" t="n">
-        <v>0.1056748838499188</v>
+        <v>0.1056748926639557</v>
       </c>
       <c r="F30" t="n">
-        <v>18.46376594161987</v>
+        <v>22.0047721862793</v>
       </c>
       <c r="G30" t="n">
-        <v>0.1584535791426897</v>
+        <v>0.1584535837173462</v>
       </c>
       <c r="H30" t="n">
         <v>0.4691900610923767</v>
@@ -1659,7 +1659,7 @@
         <v>3.118694067001343</v>
       </c>
       <c r="K30" t="n">
-        <v>1.552960000003623e-05</v>
+        <v>8.470900000247639e-06</v>
       </c>
     </row>
     <row r="31">
@@ -1675,20 +1675,20 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>-48.50</t>
+          <t>-48.50 (1.04)</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.379934819817543</v>
+        <v>0.9999253749847412</v>
       </c>
       <c r="E31" t="n">
-        <v>0.09046404175460339</v>
+        <v>0.0904640406370163</v>
       </c>
       <c r="F31" t="n">
-        <v>15.3356696395874</v>
+        <v>17.67708587646484</v>
       </c>
       <c r="G31" t="n">
-        <v>0.1412137556821108</v>
+        <v>0.1412137597799301</v>
       </c>
       <c r="H31" t="n">
         <v>1.041359066963196</v>
@@ -1700,7 +1700,7 @@
         <v>2.804337978363037</v>
       </c>
       <c r="K31" t="n">
-        <v>1.590480000004391e-05</v>
+        <v>7.383999996818602e-06</v>
       </c>
     </row>
   </sheetData>

--- a/162.xlsx
+++ b/162.xlsx
@@ -486,20 +486,20 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-37.51 (1.15)</t>
+          <t>-37.51</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.96596360206604</v>
+        <v>0.3944210809469223</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1042959839105606</v>
+        <v>0.1042959878221154</v>
       </c>
       <c r="F2" t="n">
-        <v>17.98447036743164</v>
+        <v>14.84237528991699</v>
       </c>
       <c r="G2" t="n">
-        <v>0.08318112045526505</v>
+        <v>0.08318112520128489</v>
       </c>
       <c r="H2" t="n">
         <v>0.1949195116758347</v>
@@ -511,7 +511,7 @@
         <v>1.899414658546448</v>
       </c>
       <c r="K2" t="n">
-        <v>1.509359999909066e-05</v>
+        <v>1.341890000185231e-05</v>
       </c>
     </row>
     <row r="3">
@@ -527,20 +527,20 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-37.68 (1.19)</t>
+          <t>-37.68</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.678837776184082</v>
+        <v>0.3716653314828873</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1049587205052376</v>
+        <v>0.1049587244093418</v>
       </c>
       <c r="F3" t="n">
-        <v>14.37751388549805</v>
+        <v>12.70117623138428</v>
       </c>
       <c r="G3" t="n">
-        <v>0.08636249601840973</v>
+        <v>0.08636248918622733</v>
       </c>
       <c r="H3" t="n">
         <v>1.028795123100281</v>
@@ -552,7 +552,7 @@
         <v>2.021719694137573</v>
       </c>
       <c r="K3" t="n">
-        <v>7.879100005084184e-06</v>
+        <v>9.90040000033332e-06</v>
       </c>
     </row>
     <row r="4">
@@ -568,20 +568,20 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-40.97 (0.80)</t>
+          <t>-40.97</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.572483062744141</v>
+        <v>0.5610360656678677</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1328157484531403</v>
+        <v>0.1328157481104136</v>
       </c>
       <c r="F4" t="n">
-        <v>19.05227470397949</v>
+        <v>18.21930086326599</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1076611801981926</v>
+        <v>0.1076611945927143</v>
       </c>
       <c r="H4" t="n">
         <v>0.9844127893447876</v>
@@ -593,7 +593,7 @@
         <v>2.23393440246582</v>
       </c>
       <c r="K4" t="n">
-        <v>8.027399999264163e-06</v>
+        <v>1.149710000026971e-05</v>
       </c>
     </row>
     <row r="5">
@@ -609,20 +609,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-36.80 (1.28)</t>
+          <t>-36.80</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.9875187873840332</v>
+        <v>0.3960043675899506</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1032232865691185</v>
+        <v>0.1032232804819942</v>
       </c>
       <c r="F5" t="n">
-        <v>17.244873046875</v>
+        <v>14.88078626251221</v>
       </c>
       <c r="G5" t="n">
-        <v>0.07777422666549683</v>
+        <v>0.07777422753721476</v>
       </c>
       <c r="H5" t="n">
         <v>1.018619418144226</v>
@@ -634,7 +634,7 @@
         <v>1.836353302001953</v>
       </c>
       <c r="K5" t="n">
-        <v>9.801599997445009e-06</v>
+        <v>9.152300001005642e-06</v>
       </c>
     </row>
     <row r="6">
@@ -650,20 +650,20 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-42.86 (0.68)</t>
+          <t>-42.86</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.9971363544464111</v>
+        <v>0.651809765458107</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1827750653028488</v>
+        <v>0.1827750724107027</v>
       </c>
       <c r="F6" t="n">
-        <v>24.74639129638672</v>
+        <v>21.4876535949707</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1106208264827728</v>
+        <v>0.1106208183020353</v>
       </c>
       <c r="H6" t="n">
         <v>0.6961851119995117</v>
@@ -675,7 +675,7 @@
         <v>2.534233093261719</v>
       </c>
       <c r="K6" t="n">
-        <v>8.075999998254701e-06</v>
+        <v>8.297199994558468e-06</v>
       </c>
     </row>
     <row r="7">
@@ -691,20 +691,20 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-32.15 (1.03)</t>
+          <t>-32.15</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>86.03678894042969</v>
+        <v>85.50308422851562</v>
       </c>
       <c r="E7" t="n">
-        <v>4.745238304138184</v>
+        <v>4.745238411903381</v>
       </c>
       <c r="F7" t="n">
-        <v>7468.8974609375</v>
+        <v>7397.843859863281</v>
       </c>
       <c r="G7" t="n">
-        <v>20.0107364654541</v>
+        <v>20.01073612976074</v>
       </c>
       <c r="H7" t="n">
         <v>0.7199040651321411</v>
@@ -716,7 +716,7 @@
         <v>0.6462885141372681</v>
       </c>
       <c r="K7" t="n">
-        <v>8.102299994789064e-06</v>
+        <v>8.465999999316409e-06</v>
       </c>
     </row>
     <row r="8">
@@ -732,20 +732,20 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-31.94 (1.04)</t>
+          <t>-31.94</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>84.78179168701172</v>
+        <v>84.20316628265381</v>
       </c>
       <c r="E8" t="n">
-        <v>4.714409351348877</v>
+        <v>4.714409293651581</v>
       </c>
       <c r="F8" t="n">
-        <v>7239.12109375</v>
+        <v>7146.787145996093</v>
       </c>
       <c r="G8" t="n">
-        <v>19.62985992431641</v>
+        <v>19.62985975265503</v>
       </c>
       <c r="H8" t="n">
         <v>0.7220360636711121</v>
@@ -757,7 +757,7 @@
         <v>0.6290862560272217</v>
       </c>
       <c r="K8" t="n">
-        <v>7.820099999662489e-06</v>
+        <v>8.895300001313444e-06</v>
       </c>
     </row>
     <row r="9">
@@ -773,20 +773,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-32.20 (0.97)</t>
+          <t>-32.20</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>85.07386779785156</v>
+        <v>84.27514916229248</v>
       </c>
       <c r="E9" t="n">
-        <v>4.738084316253662</v>
+        <v>4.738084337234497</v>
       </c>
       <c r="F9" t="n">
-        <v>7324.83154296875</v>
+        <v>7202.296458496094</v>
       </c>
       <c r="G9" t="n">
-        <v>20.05002784729004</v>
+        <v>20.05002739143372</v>
       </c>
       <c r="H9" t="n">
         <v>0.7181195020675659</v>
@@ -798,7 +798,7 @@
         <v>0.6569992899894714</v>
       </c>
       <c r="K9" t="n">
-        <v>8.319599997776095e-06</v>
+        <v>9.390500003064517e-06</v>
       </c>
     </row>
     <row r="10">
@@ -814,20 +814,20 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-32.07 (0.90)</t>
+          <t>-32.07</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>85.20194244384766</v>
+        <v>84.68730562591553</v>
       </c>
       <c r="E10" t="n">
-        <v>4.759157657623291</v>
+        <v>4.759157948970794</v>
       </c>
       <c r="F10" t="n">
-        <v>7317.763671875</v>
+        <v>7230.858865722656</v>
       </c>
       <c r="G10" t="n">
-        <v>19.7773494720459</v>
+        <v>19.77734749412537</v>
       </c>
       <c r="H10" t="n">
         <v>0.7185947895050049</v>
@@ -839,7 +839,7 @@
         <v>0.6297457814216614</v>
       </c>
       <c r="K10" t="n">
-        <v>8.177600000635721e-06</v>
+        <v>8.348499999556224e-06</v>
       </c>
     </row>
     <row r="11">
@@ -855,20 +855,20 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-32.13 (0.77)</t>
+          <t>-32.13</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>86.17000579833984</v>
+        <v>84.62268690490723</v>
       </c>
       <c r="E11" t="n">
-        <v>4.747989177703857</v>
+        <v>4.747989253520966</v>
       </c>
       <c r="F11" t="n">
-        <v>7406.83642578125</v>
+        <v>7175.824537109375</v>
       </c>
       <c r="G11" t="n">
-        <v>19.70671272277832</v>
+        <v>19.70671310997009</v>
       </c>
       <c r="H11" t="n">
         <v>0.7172663807868958</v>
@@ -880,7 +880,7 @@
         <v>0.612906277179718</v>
       </c>
       <c r="K11" t="n">
-        <v>8.327199997438583e-06</v>
+        <v>8.99809999827994e-06</v>
       </c>
     </row>
     <row r="12">
@@ -896,20 +896,20 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-34.47 (1.27)</t>
+          <t>-34.47</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>84.92249298095703</v>
+        <v>83.69000473022462</v>
       </c>
       <c r="E12" t="n">
-        <v>4.717652797698975</v>
+        <v>4.7176529712677</v>
       </c>
       <c r="F12" t="n">
-        <v>7239.9765625</v>
+        <v>7044.419167480469</v>
       </c>
       <c r="G12" t="n">
-        <v>19.02021598815918</v>
+        <v>19.02021579933167</v>
       </c>
       <c r="H12" t="n">
         <v>0.7194445133209229</v>
@@ -921,7 +921,7 @@
         <v>0.6798930764198303</v>
       </c>
       <c r="K12" t="n">
-        <v>8.340800006408245e-06</v>
+        <v>8.391600000322797e-06</v>
       </c>
     </row>
     <row r="13">
@@ -937,20 +937,20 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-34.42 (1.33)</t>
+          <t>-34.42</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>84.17276763916016</v>
+        <v>83.19149970245361</v>
       </c>
       <c r="E13" t="n">
-        <v>4.710550308227539</v>
+        <v>4.710550173282623</v>
       </c>
       <c r="F13" t="n">
-        <v>7076.40576171875</v>
+        <v>6934.759482421875</v>
       </c>
       <c r="G13" t="n">
-        <v>19.0302562713623</v>
+        <v>19.03025841903687</v>
       </c>
       <c r="H13" t="n">
         <v>0.718348503112793</v>
@@ -962,7 +962,7 @@
         <v>0.6647471785545349</v>
       </c>
       <c r="K13" t="n">
-        <v>8.432599999650847e-06</v>
+        <v>8.948599999712315e-06</v>
       </c>
     </row>
     <row r="14">
@@ -978,20 +978,20 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-34.32 (1.07)</t>
+          <t>-34.32</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>81.89128875732422</v>
+        <v>81.19187330627442</v>
       </c>
       <c r="E14" t="n">
-        <v>4.687593936920166</v>
+        <v>4.687594055652618</v>
       </c>
       <c r="F14" t="n">
-        <v>6755.34130859375</v>
+        <v>6653.133884277344</v>
       </c>
       <c r="G14" t="n">
-        <v>18.75619888305664</v>
+        <v>18.75619852638244</v>
       </c>
       <c r="H14" t="n">
         <v>0.7167642116546631</v>
@@ -1003,7 +1003,7 @@
         <v>0.6927752494812012</v>
       </c>
       <c r="K14" t="n">
-        <v>8.23149999632733e-06</v>
+        <v>9.863300001597962e-06</v>
       </c>
     </row>
     <row r="15">
@@ -1019,20 +1019,20 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-34.46 (1.29)</t>
+          <t>-34.46</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>85.08256530761719</v>
+        <v>84.19227960968017</v>
       </c>
       <c r="E15" t="n">
-        <v>4.69942569732666</v>
+        <v>4.699425678730011</v>
       </c>
       <c r="F15" t="n">
-        <v>7261.630859375</v>
+        <v>7129.119458007813</v>
       </c>
       <c r="G15" t="n">
-        <v>19.18807029724121</v>
+        <v>19.18807070350647</v>
       </c>
       <c r="H15" t="n">
         <v>0.7159428000450134</v>
@@ -1044,7 +1044,7 @@
         <v>0.6775802373886108</v>
       </c>
       <c r="K15" t="n">
-        <v>8.684100001119077e-06</v>
+        <v>9.147599994321354e-06</v>
       </c>
     </row>
     <row r="16">
@@ -1060,20 +1060,20 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-34.47 (1.28)</t>
+          <t>-34.47</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>84.13075256347656</v>
+        <v>83.32168952941895</v>
       </c>
       <c r="E16" t="n">
-        <v>4.703958511352539</v>
+        <v>4.703958561420441</v>
       </c>
       <c r="F16" t="n">
-        <v>7166.01904296875</v>
+        <v>7018.469251953125</v>
       </c>
       <c r="G16" t="n">
-        <v>19.135009765625</v>
+        <v>19.13500893974304</v>
       </c>
       <c r="H16" t="n">
         <v>0.7165584564208984</v>
@@ -1085,7 +1085,7 @@
         <v>0.6975191235542297</v>
       </c>
       <c r="K16" t="n">
-        <v>8.469300002616365e-06</v>
+        <v>9.622099998523482e-06</v>
       </c>
     </row>
     <row r="17">
@@ -1101,20 +1101,20 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-34.49 (1.42)</t>
+          <t>-34.49</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.5952963829040527</v>
+        <v>0.2466912651956081</v>
       </c>
       <c r="E17" t="n">
-        <v>0.04840697348117828</v>
+        <v>0.04840697149932385</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6512069702148438</v>
+        <v>0.1889150236845016</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0003086223441641778</v>
+        <v>0.0003086223388163489</v>
       </c>
       <c r="H17" t="n">
         <v>0.07230685651302338</v>
@@ -1126,7 +1126,7 @@
         <v>0.8259356021881104</v>
       </c>
       <c r="K17" t="n">
-        <v>1.723109999875305e-05</v>
+        <v>1.649720000568777e-05</v>
       </c>
     </row>
     <row r="18">
@@ -1142,20 +1142,20 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-34.17 (0.46)</t>
+          <t>-34.17</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.6545140147209167</v>
+        <v>0.4181239830553531</v>
       </c>
       <c r="E18" t="n">
-        <v>0.05324654653668404</v>
+        <v>0.05324654508009553</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8201408386230469</v>
+        <v>0.6792677726745605</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0007568926666863263</v>
+        <v>0.0007568926456442568</v>
       </c>
       <c r="H18" t="n">
         <v>0.06854981184005737</v>
@@ -1167,7 +1167,7 @@
         <v>0.7692122459411621</v>
       </c>
       <c r="K18" t="n">
-        <v>1.497709999966901e-05</v>
+        <v>1.701750000211177e-05</v>
       </c>
     </row>
     <row r="19">
@@ -1183,20 +1183,20 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-34.40 (1.11)</t>
+          <t>-34.40</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.5810646414756775</v>
+        <v>0.2621413843035698</v>
       </c>
       <c r="E19" t="n">
-        <v>0.04941532015800476</v>
+        <v>0.04941532082855701</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6877403259277344</v>
+        <v>0.4422568576335907</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0007793494150973856</v>
+        <v>0.0007793494511279278</v>
       </c>
       <c r="H19" t="n">
         <v>0.06968240439891815</v>
@@ -1208,7 +1208,7 @@
         <v>0.7609123587608337</v>
       </c>
       <c r="K19" t="n">
-        <v>1.547929999651387e-05</v>
+        <v>1.553659999626689e-05</v>
       </c>
     </row>
     <row r="20">
@@ -1224,20 +1224,20 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-34.99 (1.35)</t>
+          <t>-34.99</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.6882423758506775</v>
+        <v>0.2952102217525244</v>
       </c>
       <c r="E20" t="n">
-        <v>0.04976234585046768</v>
+        <v>0.04976234791055321</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4388465881347656</v>
+        <v>0.1777613739967346</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0002122677688021213</v>
+        <v>0.00021226779439246</v>
       </c>
       <c r="H20" t="n">
         <v>0.0725826621055603</v>
@@ -1249,7 +1249,7 @@
         <v>0.8261111378669739</v>
       </c>
       <c r="K20" t="n">
-        <v>1.500880000094185e-05</v>
+        <v>1.566099999763537e-05</v>
       </c>
     </row>
     <row r="21">
@@ -1265,20 +1265,20 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-34.41 (0.34)</t>
+          <t>-34.41</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.6090268492698669</v>
+        <v>0.2937943091094494</v>
       </c>
       <c r="E21" t="n">
-        <v>0.05173289030790329</v>
+        <v>0.05173289460688829</v>
       </c>
       <c r="F21" t="n">
-        <v>0.88250732421875</v>
+        <v>0.6190450744628906</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0005299569456838071</v>
+        <v>0.0005299569150665775</v>
       </c>
       <c r="H21" t="n">
         <v>0.06969688087701797</v>
@@ -1290,7 +1290,7 @@
         <v>0.7763814330101013</v>
       </c>
       <c r="K21" t="n">
-        <v>1.587709999876097e-05</v>
+        <v>1.600880000478355e-05</v>
       </c>
     </row>
     <row r="22">
@@ -1306,20 +1306,20 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-8.20 (0.08)</t>
+          <t>-8.20</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1.432988882064819</v>
+        <v>0.6064836847782135</v>
       </c>
       <c r="E22" t="n">
-        <v>0.04169116169214249</v>
+        <v>0.04169116235151887</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3640086650848389</v>
+        <v>0.08561419242620469</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0001154186757048592</v>
+        <v>0.0001154186749081418</v>
       </c>
       <c r="H22" t="n">
         <v>0.04552223905920982</v>
@@ -1331,7 +1331,7 @@
         <v>0.6375079751014709</v>
       </c>
       <c r="K22" t="n">
-        <v>1.472459999786224e-05</v>
+        <v>1.568379999662284e-05</v>
       </c>
     </row>
     <row r="23">
@@ -1347,20 +1347,20 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-7.00 (0.06)</t>
+          <t>-7.00</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1.532139778137207</v>
+        <v>1.030174807071686</v>
       </c>
       <c r="E23" t="n">
-        <v>0.04291481897234917</v>
+        <v>0.04291481583192944</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4306063652038574</v>
+        <v>0.09767026370763779</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0001140713502536528</v>
+        <v>0.0001140713521162979</v>
       </c>
       <c r="H23" t="n">
         <v>0.05051264539361</v>
@@ -1372,7 +1372,7 @@
         <v>0.6591068506240845</v>
       </c>
       <c r="K23" t="n">
-        <v>1.569920000474667e-05</v>
+        <v>1.600170000165235e-05</v>
       </c>
     </row>
     <row r="24">
@@ -1388,20 +1388,20 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-7.62 (0.19)</t>
+          <t>-7.62</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1.460663795471191</v>
+        <v>0.686611274600029</v>
       </c>
       <c r="E24" t="n">
-        <v>0.04401947557926178</v>
+        <v>0.04401947408914566</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1893651485443115</v>
+        <v>0.03567489624023437</v>
       </c>
       <c r="G24" t="n">
-        <v>4.119665391044691e-05</v>
+        <v>4.119664989411831e-05</v>
       </c>
       <c r="H24" t="n">
         <v>0.05103453621268272</v>
@@ -1413,7 +1413,7 @@
         <v>0.6344265937805176</v>
       </c>
       <c r="K24" t="n">
-        <v>1.529560000199126e-05</v>
+        <v>1.610629999777302e-05</v>
       </c>
     </row>
     <row r="25">
@@ -1429,20 +1429,20 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-6.24 (0.30)</t>
+          <t>-6.24</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1.564711093902588</v>
+        <v>0.6505242031216621</v>
       </c>
       <c r="E25" t="n">
-        <v>0.04108690842986107</v>
+        <v>0.04108691008761525</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2898274660110474</v>
+        <v>0.0518247749209404</v>
       </c>
       <c r="G25" t="n">
-        <v>6.130744441179559e-05</v>
+        <v>6.130743998983234e-05</v>
       </c>
       <c r="H25" t="n">
         <v>0.04903533309698105</v>
@@ -1454,7 +1454,7 @@
         <v>0.7032672762870789</v>
       </c>
       <c r="K25" t="n">
-        <v>1.457149999623653e-05</v>
+        <v>1.556339999660849e-05</v>
       </c>
     </row>
     <row r="26">
@@ -1470,20 +1470,20 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-8.77 (0.09)</t>
+          <t>-8.77</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1.395487308502197</v>
+        <v>0.7081052532196045</v>
       </c>
       <c r="E26" t="n">
-        <v>0.04439558088779449</v>
+        <v>0.04439557975158095</v>
       </c>
       <c r="F26" t="n">
-        <v>0.370948314666748</v>
+        <v>0.05564244824647904</v>
       </c>
       <c r="G26" t="n">
-        <v>5.735258673666976e-05</v>
+        <v>5.735258352797246e-05</v>
       </c>
       <c r="H26" t="n">
         <v>0.05177820101380348</v>
@@ -1495,7 +1495,7 @@
         <v>0.7030646800994873</v>
       </c>
       <c r="K26" t="n">
-        <v>1.506720000179484e-05</v>
+        <v>1.599529999657534e-05</v>
       </c>
     </row>
     <row r="27">
@@ -1511,20 +1511,20 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-43.67 (0.98)</t>
+          <t>-43.67</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.9956388473510742</v>
+        <v>0.5509438116550446</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1138138994574547</v>
+        <v>0.1138138962313533</v>
       </c>
       <c r="F27" t="n">
-        <v>17.18492126464844</v>
+        <v>16.06996207809448</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1592735648155212</v>
+        <v>0.159273573577404</v>
       </c>
       <c r="H27" t="n">
         <v>0.9768306612968445</v>
@@ -1536,7 +1536,7 @@
         <v>3.303707122802734</v>
       </c>
       <c r="K27" t="n">
-        <v>1.741729999775998e-05</v>
+        <v>7.433099999616388e-06</v>
       </c>
     </row>
     <row r="28">
@@ -1552,20 +1552,20 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-48.33 (1.14)</t>
+          <t>-48.33</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.6411409378051758</v>
+        <v>0.5882579138278962</v>
       </c>
       <c r="E28" t="n">
-        <v>0.08680037409067154</v>
+        <v>0.08680037485063076</v>
       </c>
       <c r="F28" t="n">
-        <v>17.94316101074219</v>
+        <v>15.59637615776062</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1470350921154022</v>
+        <v>0.1470350993275642</v>
       </c>
       <c r="H28" t="n">
         <v>1.045491933822632</v>
@@ -1577,7 +1577,7 @@
         <v>2.807586193084717</v>
       </c>
       <c r="K28" t="n">
-        <v>8.950399998866487e-06</v>
+        <v>8.788599996478297e-06</v>
       </c>
     </row>
     <row r="29">
@@ -1593,20 +1593,20 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>-48.10 (1.04)</t>
+          <t>-48.10</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.8933286666870117</v>
+        <v>0.5766609728336334</v>
       </c>
       <c r="E29" t="n">
-        <v>0.08606120944023132</v>
+        <v>0.08606121307611465</v>
       </c>
       <c r="F29" t="n">
-        <v>17.45991706848145</v>
+        <v>15.22148032188415</v>
       </c>
       <c r="G29" t="n">
-        <v>0.1455959677696228</v>
+        <v>0.1455959653407335</v>
       </c>
       <c r="H29" t="n">
         <v>1.044873833656311</v>
@@ -1618,7 +1618,7 @@
         <v>2.807583093643188</v>
       </c>
       <c r="K29" t="n">
-        <v>7.887599997047801e-06</v>
+        <v>8.540900002117269e-06</v>
       </c>
     </row>
     <row r="30">
@@ -1634,20 +1634,20 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>-45.40 (1.14)</t>
+          <t>-45.40</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.8894774913787842</v>
+        <v>0.5920081272125244</v>
       </c>
       <c r="E30" t="n">
-        <v>0.1056748926639557</v>
+        <v>0.1056748838499188</v>
       </c>
       <c r="F30" t="n">
-        <v>22.0047721862793</v>
+        <v>18.46376594161987</v>
       </c>
       <c r="G30" t="n">
-        <v>0.1584535837173462</v>
+        <v>0.1584535791426897</v>
       </c>
       <c r="H30" t="n">
         <v>0.4691900610923767</v>
@@ -1659,7 +1659,7 @@
         <v>3.118694067001343</v>
       </c>
       <c r="K30" t="n">
-        <v>8.470900000247639e-06</v>
+        <v>1.010210000094958e-05</v>
       </c>
     </row>
     <row r="31">
@@ -1675,20 +1675,20 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>-48.50 (1.04)</t>
+          <t>-48.50</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.9999253749847412</v>
+        <v>0.379934819817543</v>
       </c>
       <c r="E31" t="n">
-        <v>0.0904640406370163</v>
+        <v>0.09046404175460339</v>
       </c>
       <c r="F31" t="n">
-        <v>17.67708587646484</v>
+        <v>15.3356696395874</v>
       </c>
       <c r="G31" t="n">
-        <v>0.1412137597799301</v>
+        <v>0.1412137556821108</v>
       </c>
       <c r="H31" t="n">
         <v>1.041359066963196</v>
@@ -1700,7 +1700,7 @@
         <v>2.804337978363037</v>
       </c>
       <c r="K31" t="n">
-        <v>7.383999996818602e-06</v>
+        <v>7.351599997491576e-06</v>
       </c>
     </row>
   </sheetData>
